--- a/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_osc_vs_flt_ctl&gain_250407.xlsx
+++ b/XD_JIG/XD12/XD12_PWM_Rev_1/측정자료/xd12_pwm_osc_vs_flt_ctl&gain_250407.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\working\01_Project\Jig\XD_JIG\XD12\XD12_PWM_Rev_1\측정자료\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F9B8C49-C7A0-4361-AB66-E30441059A62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62A44178-5632-4566-8C02-8292B2F0B36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="43080" yWindow="4095" windowWidth="29040" windowHeight="15720" xr2:uid="{801B3258-3941-40DC-B96A-8112EB2144AA}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="6">
   <si>
     <t>FTL_CTL</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -55,6 +55,10 @@
   </si>
   <si>
     <t>#3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -79,7 +83,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -89,6 +93,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -107,15 +117,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -451,79 +464,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4898C20-7A45-46B9-8C60-3904503E94D5}">
-  <dimension ref="B2:J7"/>
+  <dimension ref="B2:J15"/>
   <sheetFormatPr defaultRowHeight="16.899999999999999" x14ac:dyDescent="0.6"/>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.6">
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="J2" s="2" t="s">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="2"/>
+      <c r="J2" s="1" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.6">
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>0</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>3</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.6">
-      <c r="B4">
+      <c r="B4" s="2">
         <v>0</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>9.18</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4" s="1">
         <v>7.76</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4" s="1">
         <v>7.28</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="1">
         <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.6">
-      <c r="B5">
+      <c r="B5" s="2">
         <v>1</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="1">
         <v>6.6</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5" s="1">
         <v>6.12</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="1">
         <v>8.16</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="1">
         <v>5.24</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.6">
-      <c r="B6">
+      <c r="B6" s="2">
         <v>2</v>
       </c>
       <c r="C6">
@@ -540,7 +554,7 @@
       </c>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.6">
-      <c r="B7">
+      <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7">
@@ -556,9 +570,110 @@
         <v>5.7</v>
       </c>
     </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B10" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="2"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B11" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="2">
+        <v>0</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>2</v>
+      </c>
+      <c r="F11" s="2">
+        <v>3</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="1">
+        <v>1</v>
+      </c>
+      <c r="D12" s="1">
+        <v>0.91500000000000004</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="F12" s="1">
+        <v>0.70499999999999996</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B13" s="2">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>0.51</v>
+      </c>
+      <c r="D13" s="1">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="E13">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="F13">
+        <v>0.89</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B14" s="2">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>0.95</v>
+      </c>
+      <c r="D14">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="E14">
+        <v>0.88</v>
+      </c>
+      <c r="F14">
+        <v>0.60499999999999998</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.6">
+      <c r="B15" s="2">
+        <v>3</v>
+      </c>
+      <c r="C15">
+        <v>0.88500000000000001</v>
+      </c>
+      <c r="D15">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="E15">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="F15">
+        <v>0.80500000000000005</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C10:F10"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
